--- a/data/trans_orig/P22_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P22_R-Clase-trans_orig.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46382</t>
+          <t>49175</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77119</t>
+          <t>77373</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27926</t>
+          <t>28637</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50994</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84075</t>
+          <t>83649</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122494</t>
+          <t>120086</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37461</t>
+          <t>37306</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64917</t>
+          <t>64781</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22407</t>
+          <t>21696</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43534</t>
+          <t>43558</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65676</t>
+          <t>66385</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98091</t>
+          <t>100055</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>342977</t>
+          <t>341633</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>377021</t>
+          <t>378931</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>220102</t>
+          <t>221336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>249791</t>
+          <t>249232</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>573745</t>
+          <t>573177</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>620195</t>
+          <t>620180</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25678</t>
+          <t>27003</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51737</t>
+          <t>53936</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24965</t>
+          <t>25376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47682</t>
+          <t>47480</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57891</t>
+          <t>57618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91736</t>
+          <t>91110</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33302</t>
+          <t>32902</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58369</t>
+          <t>57853</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31569</t>
+          <t>30386</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50527</t>
+          <t>49481</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>82165</t>
+          <t>81425</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>266400</t>
+          <t>264826</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>299716</t>
+          <t>299369</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>299764</t>
+          <t>301227</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>328991</t>
+          <t>328989</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>578445</t>
+          <t>578752</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>622421</t>
+          <t>623580</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,4%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24604</t>
+          <t>24039</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48819</t>
+          <t>48382</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>27765</t>
+          <t>25566</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>51912</t>
+          <t>50430</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14173</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19488</t>
+          <t>18658</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>488966</t>
+          <t>488985</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>513793</t>
+          <t>514346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>150556</t>
+          <t>150647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>163279</t>
+          <t>163006</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>646554</t>
+          <t>646903</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>673525</t>
+          <t>675001</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>12200</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43120</t>
+          <t>43261</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>72556</t>
+          <t>72758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19606</t>
+          <t>18916</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>40118</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69120</t>
+          <t>69330</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>105380</t>
+          <t>104358</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>12162</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30039</t>
+          <t>30607</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18945</t>
+          <t>20467</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>41127</t>
+          <t>41574</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1145314</t>
+          <t>1146368</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1178131</t>
+          <t>1180423</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>649158</t>
+          <t>650771</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>677948</t>
+          <t>678256</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1809736</t>
+          <t>1809825</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1849125</t>
+          <t>1849994</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27213</t>
+          <t>26946</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24423</t>
+          <t>25427</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22162</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>46412</t>
+          <t>46994</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17154</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12213</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30541</t>
+          <t>31422</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19584</t>
+          <t>19315</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43392</t>
+          <t>42350</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>309913</t>
+          <t>309739</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>331554</t>
+          <t>331303</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>519361</t>
+          <t>519013</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>544595</t>
+          <t>542791</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>837535</t>
+          <t>836722</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>872077</t>
+          <t>870707</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11158</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>42037</t>
+          <t>40813</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>69549</t>
+          <t>69543</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>47396</t>
+          <t>46931</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>79392</t>
+          <t>77518</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>19961</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>35291</t>
+          <t>35409</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>62378</t>
+          <t>62832</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>45475</t>
+          <t>44472</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>76484</t>
+          <t>74508</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>270343</t>
+          <t>270620</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>285973</t>
+          <t>287074</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1123256</t>
+          <t>1120845</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1161286</t>
+          <t>1159144</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1395363</t>
+          <t>1400792</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1439693</t>
+          <t>1443797</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1654</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>16585</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>17087</t>
+          <t>18166</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>187829</t>
+          <t>189752</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>244225</t>
+          <t>247343</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>152552</t>
+          <t>151433</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>202274</t>
+          <t>203517</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>349136</t>
+          <t>350313</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>430768</t>
+          <t>432066</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>106838</t>
+          <t>104498</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>150242</t>
+          <t>150369</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>123250</t>
+          <t>123933</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>171256</t>
+          <t>169934</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>243216</t>
+          <t>244907</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>308358</t>
+          <t>311457</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2876168</t>
+          <t>2879033</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2947768</t>
+          <t>2947477</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3016198</t>
+          <t>3018565</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3088499</t>
+          <t>3085353</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5920486</t>
+          <t>5915381</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6019010</t>
+          <t>6013743</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -5063,12 +5063,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31884</t>
+          <t>30402</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59201</t>
+          <t>57776</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25351</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48574</t>
+          <t>47936</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62443</t>
+          <t>61649</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98023</t>
+          <t>98641</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5176,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43912</t>
+          <t>42779</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75275</t>
+          <t>73770</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22149</t>
+          <t>22532</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44229</t>
+          <t>45151</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71434</t>
+          <t>69725</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109083</t>
+          <t>109325</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>317569</t>
+          <t>317515</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>353593</t>
+          <t>355083</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>231424</t>
+          <t>230833</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>261999</t>
+          <t>260454</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>559942</t>
+          <t>557637</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>606714</t>
+          <t>606734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25260</t>
+          <t>25020</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50188</t>
+          <t>48923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21330</t>
+          <t>21194</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45135</t>
+          <t>43973</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51624</t>
+          <t>52702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84690</t>
+          <t>86074</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55286</t>
+          <t>55994</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91857</t>
+          <t>92882</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14405</t>
+          <t>15615</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37806</t>
+          <t>38373</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77973</t>
+          <t>76509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>121637</t>
+          <t>120192</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>290104</t>
+          <t>288771</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>330471</t>
+          <t>329879</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>264837</t>
+          <t>264553</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>296512</t>
+          <t>295523</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>565512</t>
+          <t>564171</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>615700</t>
+          <t>615163</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17292</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39244</t>
+          <t>38369</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>19672</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>27147</t>
+          <t>27432</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>52088</t>
+          <t>53440</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13297</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17719</t>
+          <t>16244</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>23839</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>582382</t>
+          <t>584374</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>606620</t>
+          <t>607910</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>230861</t>
+          <t>230862</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>248579</t>
+          <t>248352</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>820472</t>
+          <t>822095</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>851285</t>
+          <t>851694</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27345</t>
+          <t>28087</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51708</t>
+          <t>53522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19933</t>
+          <t>19273</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42553</t>
+          <t>41105</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53703</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84473</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26082</t>
+          <t>25083</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11954</t>
+          <t>13221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>32162</t>
+          <t>32699</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1100080</t>
+          <t>1098994</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1125975</t>
+          <t>1125875</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>704991</t>
+          <t>705504</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>733178</t>
+          <t>733414</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1814265</t>
+          <t>1814427</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1852418</t>
+          <t>1853194</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>9297</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14692</t>
+          <t>14901</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19894</t>
+          <t>19790</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11947</t>
+          <t>11957</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28848</t>
+          <t>29255</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9026</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>16822</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>21342</t>
+          <t>21668</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>488504</t>
+          <t>487764</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>502972</t>
+          <t>502947</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>731440</t>
+          <t>730929</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>748880</t>
+          <t>748917</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1224192</t>
+          <t>1224028</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1247624</t>
+          <t>1248132</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11819</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20564</t>
+          <t>20920</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45336</t>
+          <t>44957</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25589</t>
+          <t>25986</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>51325</t>
+          <t>51456</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>23651</t>
+          <t>23900</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>22013</t>
+          <t>22037</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>47178</t>
+          <t>46340</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>34603</t>
+          <t>33155</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>63777</t>
+          <t>62667</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>235235</t>
+          <t>235050</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>254267</t>
+          <t>254248</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1027853</t>
+          <t>1028672</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1060302</t>
+          <t>1060991</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1271639</t>
+          <t>1270363</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1308826</t>
+          <t>1310316</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11891</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>12334</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>134151</t>
+          <t>133655</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>185521</t>
+          <t>185762</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>124887</t>
+          <t>126579</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>175643</t>
+          <t>178631</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>269910</t>
+          <t>270117</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>345380</t>
+          <t>344584</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>130588</t>
+          <t>131005</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>187496</t>
+          <t>187239</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>102372</t>
+          <t>99481</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>147698</t>
+          <t>148324</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>247122</t>
+          <t>244017</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>319023</t>
+          <t>318806</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3062266</t>
+          <t>3066431</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3137586</t>
+          <t>3137086</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3240946</t>
+          <t>3241513</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3308603</t>
+          <t>3311319</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6327874</t>
+          <t>6327312</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6430413</t>
+          <t>6430771</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29169</t>
+          <t>30495</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54678</t>
+          <t>56398</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>39319</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66342</t>
+          <t>66896</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77580</t>
+          <t>75499</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116380</t>
+          <t>112711</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -9393,12 +9393,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51425</t>
+          <t>50162</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>81854</t>
+          <t>81332</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30802</t>
+          <t>30830</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55493</t>
+          <t>56219</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88105</t>
+          <t>89481</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>128346</t>
+          <t>127903</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -9506,12 +9506,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>303008</t>
+          <t>299424</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>338747</t>
+          <t>338250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>236989</t>
+          <t>235819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>270322</t>
+          <t>269007</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>547745</t>
+          <t>550749</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>598638</t>
+          <t>598820</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -9849,12 +9849,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34397</t>
+          <t>34630</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24585</t>
+          <t>24374</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47397</t>
+          <t>47566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42850</t>
+          <t>43866</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74659</t>
+          <t>73565</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -9962,12 +9962,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42401</t>
+          <t>43272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72344</t>
+          <t>70812</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17634</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37957</t>
+          <t>38081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67696</t>
+          <t>68073</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102600</t>
+          <t>104895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -10075,12 +10075,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>278028</t>
+          <t>280940</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>312611</t>
+          <t>311616</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>297161</t>
+          <t>294459</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>324959</t>
+          <t>323634</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>583578</t>
+          <t>579988</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>627538</t>
+          <t>626791</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,74%</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -10418,12 +10418,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24697</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10433,12 +10433,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>14203</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>32849</t>
+          <t>34315</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10704</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>15678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -10644,12 +10644,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>489605</t>
+          <t>490845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509870</t>
+          <t>509309</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10659,12 +10659,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145501</t>
+          <t>146104</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159269</t>
+          <t>159471</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>642555</t>
+          <t>640790</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>665850</t>
+          <t>665788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>849</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -10987,12 +10987,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>11833</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29750</t>
+          <t>30336</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29073</t>
+          <t>29431</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>27687</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>52506</t>
+          <t>53351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11072,12 +11072,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -11100,12 +11100,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>10436</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29709</t>
+          <t>29345</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11135,12 +11135,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9810</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>25986</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11150,47 +11150,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>34563</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>23364</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>48216</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>34563</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>23156</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>48570</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1094179</t>
+          <t>1094666</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1120190</t>
+          <t>1121445</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>772691</t>
+          <t>773622</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>796481</t>
+          <t>797859</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11263,12 +11263,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1873801</t>
+          <t>1874802</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1910439</t>
+          <t>1909576</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14548</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21764</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12431</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31063</t>
+          <t>30639</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -11669,12 +11669,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>11309</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15285</t>
+          <t>14953</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -11782,12 +11782,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>600532</t>
+          <t>600199</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>613440</t>
+          <t>613367</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11797,12 +11797,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>710108</t>
+          <t>709598</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>727490</t>
+          <t>727647</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11832,12 +11832,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1315057</t>
+          <t>1316868</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1337946</t>
+          <t>1338267</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12032,7 +12032,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -12125,12 +12125,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21956</t>
+          <t>22382</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12160,12 +12160,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18298</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40262</t>
+          <t>40386</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12195,12 +12195,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>28523</t>
+          <t>29223</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>55365</t>
+          <t>56927</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -12238,12 +12238,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12273,12 +12273,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17522</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>39883</t>
+          <t>39893</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -12308,12 +12308,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>26051</t>
+          <t>26225</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>51815</t>
+          <t>50085</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -12351,12 +12351,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>252842</t>
+          <t>252626</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>271287</t>
+          <t>271627</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1007915</t>
+          <t>1008447</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1038243</t>
+          <t>1039397</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1267895</t>
+          <t>1267339</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1304282</t>
+          <t>1304867</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -12581,12 +12581,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15524</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>850</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12651,12 +12651,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>18914</t>
+          <t>19160</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12666,12 +12666,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -12694,12 +12694,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>98162</t>
+          <t>99435</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>143544</t>
+          <t>142871</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12729,12 +12729,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>127687</t>
+          <t>127770</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>181734</t>
+          <t>176972</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12764,12 +12764,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>243868</t>
+          <t>236729</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>308022</t>
+          <t>303209</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -12807,12 +12807,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>131508</t>
+          <t>132073</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>183563</t>
+          <t>183154</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>98730</t>
+          <t>100327</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>144439</t>
+          <t>146015</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>242873</t>
+          <t>244728</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>310828</t>
+          <t>313814</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12892,12 +12892,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3059630</t>
+          <t>3068480</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3130168</t>
+          <t>3132015</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3213944</t>
+          <t>3215690</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3280655</t>
+          <t>3280598</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6302538</t>
+          <t>6301078</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6394060</t>
+          <t>6391155</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -13492,32 +13492,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>105068</t>
+          <t>115834</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87221</t>
+          <t>96132</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>124175</t>
+          <t>135171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13527,32 +13527,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>118275</t>
+          <t>128837</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103851</t>
+          <t>110557</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135040</t>
+          <t>145177</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13562,32 +13562,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>223343</t>
+          <t>244671</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>200363</t>
+          <t>220530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>246630</t>
+          <t>270583</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -13605,32 +13605,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45730</t>
+          <t>47616</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34925</t>
+          <t>36130</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60055</t>
+          <t>63428</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13640,32 +13640,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42065</t>
+          <t>45171</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33010</t>
+          <t>35314</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52191</t>
+          <t>56465</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13675,32 +13675,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>87796</t>
+          <t>92788</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>73643</t>
+          <t>78434</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>107410</t>
+          <t>111652</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -13718,32 +13718,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>354414</t>
+          <t>387168</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>331720</t>
+          <t>365030</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>375039</t>
+          <t>407956</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13753,32 +13753,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>287127</t>
+          <t>314402</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>269492</t>
+          <t>296587</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>303087</t>
+          <t>334718</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13788,32 +13788,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>641541</t>
+          <t>701570</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>615581</t>
+          <t>673580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>669439</t>
+          <t>727540</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,02%</t>
         </is>
       </c>
     </row>
@@ -13831,17 +13831,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13866,17 +13866,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13901,17 +13901,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>441</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -13993,12 +13993,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>441</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -14061,32 +14061,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>93909</t>
+          <t>96655</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77486</t>
+          <t>78929</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115958</t>
+          <t>118878</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14096,32 +14096,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>77653</t>
+          <t>86495</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64503</t>
+          <t>72556</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91519</t>
+          <t>99557</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14131,32 +14131,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>171562</t>
+          <t>183150</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150222</t>
+          <t>161165</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196275</t>
+          <t>208285</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -14174,32 +14174,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48287</t>
+          <t>52552</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36641</t>
+          <t>39237</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63255</t>
+          <t>67997</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14209,32 +14209,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>21063</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13592</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27861</t>
+          <t>29565</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14244,32 +14244,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>68370</t>
+          <t>73615</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54797</t>
+          <t>58765</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85048</t>
+          <t>90168</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -14287,32 +14287,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>310017</t>
+          <t>334005</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>286583</t>
+          <t>312797</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>331463</t>
+          <t>355430</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14322,32 +14322,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>284429</t>
+          <t>315144</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>270035</t>
+          <t>300215</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>298459</t>
+          <t>329663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14357,32 +14357,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>594446</t>
+          <t>649149</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>568842</t>
+          <t>619725</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>618019</t>
+          <t>673369</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,29%</t>
         </is>
       </c>
     </row>
@@ -14400,17 +14400,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14435,17 +14435,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14470,17 +14470,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14630,32 +14630,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29136</t>
+          <t>33580</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>24052</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51940</t>
+          <t>48087</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14665,32 +14665,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>18970</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>12485</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22513</t>
+          <t>26154</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14700,32 +14700,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>45245</t>
+          <t>52549</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19440</t>
+          <t>39866</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>69510</t>
+          <t>66706</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -14743,7 +14743,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -14753,12 +14753,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>11420</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14778,32 +14778,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14813,32 +14813,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -14856,32 +14856,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>638964</t>
+          <t>435686</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>615913</t>
+          <t>420504</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>657867</t>
+          <t>446133</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14891,32 +14891,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>148406</t>
+          <t>166107</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141718</t>
+          <t>158383</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153847</t>
+          <t>172734</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -14926,32 +14926,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>787369</t>
+          <t>601793</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>762301</t>
+          <t>586338</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>814149</t>
+          <t>615410</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -14969,17 +14969,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15004,17 +15004,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -15096,12 +15096,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -15166,12 +15166,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -15199,32 +15199,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>48995</t>
+          <t>54976</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35388</t>
+          <t>40710</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64244</t>
+          <t>71811</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15234,32 +15234,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>65690</t>
+          <t>74340</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37259</t>
+          <t>60701</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>91047</t>
+          <t>92595</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15269,32 +15269,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>114684</t>
+          <t>129316</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>79496</t>
+          <t>108849</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>141352</t>
+          <t>153756</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -15312,32 +15312,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>27081</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15347,32 +15347,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>12660</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15382,32 +15382,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>12166</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25429</t>
+          <t>36739</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -15425,32 +15425,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>976615</t>
+          <t>1063231</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>958276</t>
+          <t>1045261</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>990851</t>
+          <t>1080988</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15460,32 +15460,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>905270</t>
+          <t>779409</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>878548</t>
+          <t>762623</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>939746</t>
+          <t>794928</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15495,32 +15495,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1881884</t>
+          <t>1842641</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1854157</t>
+          <t>1816796</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1919802</t>
+          <t>1866060</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -15538,17 +15538,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15573,17 +15573,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15608,17 +15608,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15655,7 +15655,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>899</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -15665,12 +15665,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15690,32 +15690,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10371</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>10436</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -15768,32 +15768,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>17707</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10060</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27222</t>
+          <t>28790</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15803,32 +15803,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>28022</t>
+          <t>29675</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>21344</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39480</t>
+          <t>40480</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15838,32 +15838,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>44943</t>
+          <t>47382</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32271</t>
+          <t>35832</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59458</t>
+          <t>62386</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15916,12 +15916,12 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -15931,17 +15931,17 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15951,32 +15951,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -15994,32 +15994,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>456327</t>
+          <t>546828</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>445789</t>
+          <t>534488</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>463568</t>
+          <t>555436</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16029,32 +16029,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>804449</t>
+          <t>792979</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>791563</t>
+          <t>781807</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>814262</t>
+          <t>802292</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16064,32 +16064,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1260775</t>
+          <t>1339807</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1245336</t>
+          <t>1324044</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1274335</t>
+          <t>1352838</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -16107,17 +16107,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16142,17 +16142,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16177,17 +16177,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16209,7 +16209,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -16234,12 +16234,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16259,7 +16259,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16294,32 +16294,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>11173</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -16337,32 +16337,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>17269</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34519</t>
+          <t>37482</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16372,32 +16372,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>37543</t>
+          <t>39523</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26796</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>50706</t>
+          <t>54912</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16407,32 +16407,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>54812</t>
+          <t>57089</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39718</t>
+          <t>41329</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>77213</t>
+          <t>78423</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -16450,32 +16450,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10991</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27577</t>
+          <t>24751</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16485,32 +16485,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>16814</t>
+          <t>18131</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>25739</t>
+          <t>26167</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16520,32 +16520,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>27805</t>
+          <t>28334</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>17797</t>
+          <t>17817</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>44859</t>
+          <t>42298</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -16563,32 +16563,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>212085</t>
+          <t>207638</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>192541</t>
+          <t>187548</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>226057</t>
+          <t>222302</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16598,32 +16598,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>705874</t>
+          <t>785322</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>691023</t>
+          <t>769509</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>718255</t>
+          <t>798270</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16633,32 +16633,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>917959</t>
+          <t>992960</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>891546</t>
+          <t>970126</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>936351</t>
+          <t>1012919</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -16676,17 +16676,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -16711,17 +16711,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -16746,17 +16746,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -16793,32 +16793,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16828,32 +16828,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>11998</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16863,32 +16863,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>19503</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -16906,32 +16906,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>311297</t>
+          <t>336318</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>249684</t>
+          <t>301843</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>356009</t>
+          <t>378172</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16941,32 +16941,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>343292</t>
+          <t>377839</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>274419</t>
+          <t>347507</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>387677</t>
+          <t>414334</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16976,32 +16976,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>654589</t>
+          <t>714157</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>557707</t>
+          <t>662282</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>717509</t>
+          <t>768657</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -17019,32 +17019,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>114489</t>
+          <t>127829</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>85599</t>
+          <t>104566</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>140934</t>
+          <t>154367</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17054,32 +17054,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>91276</t>
+          <t>97588</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>70961</t>
+          <t>82668</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>107387</t>
+          <t>114637</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17089,32 +17089,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>205765</t>
+          <t>225417</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>172090</t>
+          <t>194246</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>238388</t>
+          <t>252932</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -17132,32 +17132,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2948421</t>
+          <t>2974555</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2892616</t>
+          <t>2923194</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3034800</t>
+          <t>3020191</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17167,32 +17167,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3135553</t>
+          <t>3153364</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3087522</t>
+          <t>3114979</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3222090</t>
+          <t>3188767</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17202,32 +17202,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>6083974</t>
+          <t>6127919</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6006095</t>
+          <t>6070136</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6204171</t>
+          <t>6186589</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>87,42%</t>
         </is>
       </c>
     </row>
@@ -17245,17 +17245,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17280,17 +17280,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17315,17 +17315,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6951479</t>
+          <t>7077146</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6951479</t>
+          <t>7077146</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6951479</t>
+          <t>7077146</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
